--- a/backend/data/RAGcoon_Backend_Frontend_Update_Handoff.xlsx
+++ b/backend/data/RAGcoon_Backend_Frontend_Update_Handoff.xlsx
@@ -545,7 +545,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>อัปเดตล่าสุด: 2026-10-26 21:22 | สถานะฝั่ง RAG Engine: สร้างและทดสอบเสร็จสมบูรณ์ 100% (พร้อมเชื่อมต่อ API &amp; UI)</t>
+          <t>อัปเดตล่าสุด: 2026-10-26 21:32 | สถานะฝั่ง RAG Engine: สร้างและทดสอบเสร็จสมบูรณ์ 100% (พร้อมเชื่อมต่อ API &amp; UI)</t>
         </is>
       </c>
     </row>
